--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105246</v>
+        <v>105253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105253</v>
+        <v>105256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105256</v>
+        <v>105260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105260</v>
+        <v>105261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105261</v>
+        <v>105263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25283-2024 artfynd.xlsx
+++ b/artfynd/A 25283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125542033</v>
       </c>
       <c r="B2" t="n">
-        <v>105263</v>
+        <v>105265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
